--- a/strategy/seo-roadmap-tracker.xlsx
+++ b/strategy/seo-roadmap-tracker.xlsx
@@ -14,13 +14,15 @@
     <sheet name="Site Build" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Reviews" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Citations" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="GBP Posts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Metrics" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Waiting On Cleo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Local Citations" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="GBP Posts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Metrics" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Waiting On Cleo" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tasks'!$A$1:$L$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tasks'!$A$1:$L$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Citations'!$A$4:$J$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Local Citations'!$A$36:$K$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,7 +93,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +103,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E5DCCA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EEE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -121,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -171,6 +178,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -565,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -709,211 +729,223 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>You edit</t>
+          <t>Two citation tabs</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Status, Date done, and Notes. Leave the rest unless the plan genuinely changes.</t>
+          <t>Citations fixes the listings that exist and are wrong. Local Citations builds the ones that do not exist yet.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Blocked?</t>
+          <t>You edit</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Set Status to Blocked and write what you are waiting on in Notes. Blocked rows turn red.</t>
+          <t>Status, Date done, and Notes. Leave the rest unless the plan genuinely changes.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Blocked?</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Monday: profile insights. Wednesday: batch the content and film the reel. Friday: log the week.</t>
+          <t>Set Status to Blocked and write what you are waiting on in Notes. Blocked rows turn red.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Monday: profile insights. Wednesday: batch the content and film the reel. Friday: log the week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Fill the Metrics tab. Compare against the baseline column, not against last month.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr"/>
-    </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr"/>
+      <c r="B21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>THE TWO THINGS THAT DECIDE THIS</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Reviews</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Twelve today. The ask goes out inside 24 hours of every appointment or the number does not move.</t>
-        </is>
-      </c>
+      <c r="B22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>Reviews</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Twelve today. The ask goes out inside 24 hours of every appointment or the number does not move.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>The daily log</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Five slots a day is not a lot. Missing them for a fortnight undoes a month of the rest.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="4" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr"/>
+      <c r="B25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>WHERE THINGS STAND</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Project tasks</t>
-        </is>
-      </c>
-      <c r="B26" s="6">
-        <f>COUNTA(Tasks!F2:F149)</f>
-        <v/>
-      </c>
+      <c r="B26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Project tasks</t>
         </is>
       </c>
       <c r="B27" s="6">
-        <f>COUNTIF(Tasks!J2:J149,"Not started")</f>
+        <f>COUNTA(Tasks!F2:F156)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Not started</t>
         </is>
       </c>
       <c r="B28" s="6">
-        <f>COUNTIF(Tasks!J2:J149,"In progress")</f>
+        <f>COUNTIF(Tasks!J2:J156,"Not started")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="B29" s="6">
-        <f>COUNTIF(Tasks!J2:J149,"Blocked")</f>
+        <f>COUNTIF(Tasks!J2:J156,"In progress")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="B30" s="6">
-        <f>COUNTIF(Tasks!J2:J149,"Done")</f>
+        <f>COUNTIF(Tasks!J2:J156,"Blocked")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Overdue and not done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="B31" s="6">
-        <f>SUMPRODUCT((Tasks!D2:D149&lt;TODAY())*(Tasks!J2:J149&lt;&gt;"Done")*(Tasks!J2:J149&lt;&gt;"Not applicable"))</f>
+        <f>COUNTIF(Tasks!J2:J156,"Done")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Percent complete</t>
-        </is>
-      </c>
-      <c r="B32" s="7">
-        <f>IFERROR(COUNTIF(Tasks!J2:J149,"Done")/COUNTA(Tasks!F2:F149),0)</f>
+          <t>Overdue and not done</t>
+        </is>
+      </c>
+      <c r="B32" s="6">
+        <f>SUMPRODUCT((Tasks!D2:D156&lt;TODAY())*(Tasks!J2:J156&lt;&gt;"Done")*(Tasks!J2:J156&lt;&gt;"Not applicable"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>Percent complete</t>
+        </is>
+      </c>
+      <c r="B33" s="7">
+        <f>IFERROR(COUNTIF(Tasks!J2:J156,"Done")/COUNTA(Tasks!F2:F156),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>Daily slots done</t>
         </is>
       </c>
-      <c r="B33" s="6">
+      <c r="B34" s="6">
         <f>'Daily Log'!G2</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Daily slots missed</t>
         </is>
       </c>
-      <c r="B34" s="6">
+      <c r="B35" s="6">
         <f>'Daily Log'!I2</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Daily completion rate</t>
         </is>
       </c>
-      <c r="B35" s="7">
+      <c r="B36" s="7">
         <f>'Daily Log'!K2</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Import to Google Sheets: drive.google.com &gt; New &gt; File upload &gt; pick this file &gt; open with Google Sheets.</t>
         </is>
@@ -925,6 +957,398 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fill at the end of each month. Compare against the baseline column, not against last month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>What we track</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Baseline (17 Aug)</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Target by 14 Feb</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>End Sep</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>End Oct</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>End Nov</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>End Dec</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>End Jan</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>Mid Feb</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Google reviews</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>30 to 34, still at or near 5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Google review average</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>At or near 5.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Calls from Google profile</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Up on baseline every month</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Direction requests from Google</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Up on baseline every month</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Google profile views</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Up on baseline every month</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>GBP posts published in the month</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>20 or more, every month</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Map pack position: nurse injector oakville</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Visible in the pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Map pack position: botox oakville</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Visible in the pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Map pack position: lip filler oakville</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Visible in the pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Instagram profile visits</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Up on baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Instagram link taps</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Rising faster than profile visits</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Reels published in the month</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Four, one a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>DMs received</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Not tracked</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Tracked weekly from week 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Consultations booked</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Not tracked</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Tracked weekly, attributed to source</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Ad spend</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Not supplied</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Confirmed and split 70/20/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Cost per DM from ads</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Falling month on month</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Website sessions</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>No site</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>From launch in October, rising month on month</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Search Console impressions</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>No site</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Rising month on month from October</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Pages indexed</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>No site</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Every page, confirmed in Search Console</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Daily slot completion rate</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>85 per cent or better</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1839,7 +2263,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>One directory a day claimed or corrected until the list is clean, then one a week to keep it clean. Name, address and phone identical everywhere, no exceptions.</t>
+          <t>One directory a day. The Citations tab first — the listings that exist and are wrong — then the Local Citations build list, where there is no listing at all. Once both are clean, one a week to keep them that way. Name, address and phone identical everywhere, no exceptions.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1849,7 +2273,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Citations tab</t>
+          <t>Citations + Local Citations</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -6333,7 +6757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L149"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6981,22 +7405,22 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>Daily routine</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Start the daily routine: GBP post, Instagram, on-page, review ask, citation</t>
+          <t>Fill in THE RECORD on the Local Citations tab: one name, one address, one phone, one email</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -7036,17 +7460,17 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Agree who does which daily slot and put it in the calendar</t>
+          <t>Start the daily routine: GBP post, Instagram, on-page, review ask, citation</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -7081,17 +7505,17 @@
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Daily routine</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Record the baseline: 12 reviews, 5.0 average, GBP calls, views and direction requests</t>
+          <t>Agree who does which daily slot and put it in the calendar</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -7136,12 +7560,12 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Send us your real opening hours for every day of the week</t>
+          <t>Record the baseline: 12 reviews, 5.0 average, GBP calls, views and direction requests</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -7186,7 +7610,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Name the three competitors you want to be measured against</t>
+          <t>Send us your real opening hours for every day of the week</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -7201,7 +7625,7 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -7223,25 +7647,25 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="D18" s="22" t="n">
-        <v>46264</v>
+        <v>46257</v>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on Birdeye</t>
+          <t>Name the three competitors you want to be measured against</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -7251,7 +7675,7 @@
       </c>
       <c r="I18" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -7286,7 +7710,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on Facebook</t>
+          <t>Correct postal code to L6M 0T9 on Birdeye</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -7336,7 +7760,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on Fresha</t>
+          <t>Correct postal code to L6M 0T9 on Facebook</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -7386,7 +7810,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on Yelp.ca</t>
+          <t>Correct postal code to L6M 0T9 on Fresha</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -7401,7 +7825,7 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -7436,7 +7860,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on Yellow Pages</t>
+          <t>Correct postal code to L6M 0T9 on Yelp.ca</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -7481,17 +7905,17 @@
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>PLANNING WEEK: agree the sitemap and the full page inventory</t>
+          <t>Correct postal code to L6M 0T9 on Yellow Pages</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -7501,7 +7925,7 @@
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -7531,12 +7955,12 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Build the keyword-to-page map so every page has one job</t>
+          <t>Check which directories on the Local Citations build list are still live and still free</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -7551,7 +7975,7 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -7586,12 +8010,12 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Wireframe the home page, the contact page and the treatment page template</t>
+          <t>PLANNING WEEK: agree the sitemap and the full page inventory</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -7636,7 +8060,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Pull the brand kit — colours, type, logo — from design/brand</t>
+          <t>Build the keyword-to-page map so every page has one job</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -7651,7 +8075,7 @@
       </c>
       <c r="I26" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -7686,12 +8110,12 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Send the domain registrar login for luxurybeautybycleo.ca</t>
+          <t>Wireframe the home page, the contact page and the treatment page template</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -7736,12 +8160,12 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Send the treatment list with current pricing</t>
+          <t>Pull the brand kit — colours, type, logo — from design/brand</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -7751,7 +8175,7 @@
       </c>
       <c r="I28" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -7786,12 +8210,12 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>DESIGN REVIEW with Cleo. Sign-off due Friday 28 August</t>
+          <t>Send the domain registrar login for luxurybeautybycleo.ca</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -7831,17 +8255,17 @@
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Rewrite the Instagram name field to read 'Cleo | Nurse Injector Oakville'</t>
+          <t>Send the treatment list with current pricing</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -7881,17 +8305,17 @@
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Rewrite the Instagram bio to name the town and the treatments</t>
+          <t>DESIGN REVIEW with Cleo. Sign-off due Friday 28 August</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -7936,7 +8360,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Fix the link in bio so it no longer points at the dead domain</t>
+          <t>Rewrite the Instagram name field to read 'Cleo | Nurse Injector Oakville'</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -7986,17 +8410,17 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Start location-tagging Oakville on every post</t>
+          <t>Rewrite the Instagram bio to name the town and the treatments</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -8031,12 +8455,12 @@
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Write the WhatsApp review-ask message</t>
+          <t>Fix the link in bio so it no longer points at the dead domain</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -8081,12 +8505,12 @@
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Reply to all 12 existing reviews</t>
+          <t>Start location-tagging Oakville on every post</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -8096,12 +8520,12 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J35" s="21" t="inlineStr">
@@ -8123,25 +8547,25 @@
       </c>
       <c r="C36" s="21" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D36" s="22" t="n">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>DESIGN SIGN-OFF DUE Monday 31 August</t>
+          <t>Write the WhatsApp review-ask message</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -8173,25 +8597,25 @@
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>W3</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D37" s="22" t="n">
-        <v>46271</v>
+        <v>46264</v>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>BUILD STARTS 1 SEPTEMBER: hosting sorted, DNS pointed, platform set up</t>
+          <t>Reply to all 12 existing reviews</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -8201,7 +8625,7 @@
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J37" s="21" t="inlineStr">
@@ -8236,12 +8660,12 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Scaffold the page structure agreed in planning</t>
+          <t>DESIGN SIGN-OFF DUE Monday 31 August</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -8286,12 +8710,12 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Write the home page copy and get it approved</t>
+          <t>BUILD STARTS 1 SEPTEMBER: hosting sorted, DNS pointed, platform set up</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -8336,7 +8760,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Write the contact page copy with the corrected NAP and hours</t>
+          <t>Scaffold the page structure agreed in planning</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -8381,17 +8805,17 @@
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on Apple Maps</t>
+          <t>Write the home page copy and get it approved</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H41" s="21" t="inlineStr">
@@ -8401,7 +8825,7 @@
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J41" s="21" t="inlineStr">
@@ -8431,12 +8855,12 @@
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on Bing Places</t>
+          <t>Write the contact page copy with the corrected NAP and hours</t>
         </is>
       </c>
       <c r="G42" s="21" t="inlineStr">
@@ -8451,7 +8875,7 @@
       </c>
       <c r="I42" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J42" s="21" t="inlineStr">
@@ -8486,7 +8910,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on RateMDs</t>
+          <t>Correct postal code to L6M 0T9 on Apple Maps</t>
         </is>
       </c>
       <c r="G43" s="21" t="inlineStr">
@@ -8501,7 +8925,7 @@
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J43" s="21" t="inlineStr">
@@ -8531,12 +8955,12 @@
       </c>
       <c r="E44" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Fill out the GBP services list with a plain description of each treatment</t>
+          <t>Correct postal code to L6M 0T9 on Bing Places</t>
         </is>
       </c>
       <c r="G44" s="21" t="inlineStr">
@@ -8581,12 +9005,12 @@
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Add a working booking link to GBP</t>
+          <t>Correct postal code to L6M 0T9 on RateMDs</t>
         </is>
       </c>
       <c r="G45" s="21" t="inlineStr">
@@ -8601,7 +9025,7 @@
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J45" s="21" t="inlineStr">
@@ -8631,22 +9055,22 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Start sending the review ask within 24 hours of every appointment</t>
+          <t>Build the Oakville and Halton local citations from the build list</t>
         </is>
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H46" s="21" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I46" s="21" t="inlineStr">
@@ -8681,17 +9105,17 @@
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Google profile</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Confirm the signed before-and-after consent form is on file</t>
+          <t>Fill out the GBP services list with a plain description of each treatment</t>
         </is>
       </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H47" s="21" t="inlineStr">
@@ -8701,7 +9125,7 @@
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J47" s="21" t="inlineStr">
@@ -8723,20 +9147,20 @@
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="D48" s="22" t="n">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Google profile</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Home and contact pages complete in staging: NAP, hours, booking link, schema</t>
+          <t>Add a working booking link to GBP</t>
         </is>
       </c>
       <c r="G48" s="21" t="inlineStr">
@@ -8773,30 +9197,30 @@
       </c>
       <c r="C49" s="21" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="D49" s="22" t="n">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>LocalBusiness and Service schema on every page built so far</t>
+          <t>Start sending the review ask within 24 hours of every appointment</t>
         </is>
       </c>
       <c r="G49" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H49" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="I49" s="21" t="inlineStr">
@@ -8823,25 +9247,25 @@
       </c>
       <c r="C50" s="21" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="D50" s="22" t="n">
-        <v>46278</v>
+        <v>46271</v>
       </c>
       <c r="E50" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Title tags and meta descriptions for the home and contact pages</t>
+          <t>Confirm the signed before-and-after consent form is on file</t>
         </is>
       </c>
       <c r="G50" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H50" s="21" t="inlineStr">
@@ -8881,12 +9305,12 @@
       </c>
       <c r="E51" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Correct postal code to L6M 0T9 on the Canadian chamber directories</t>
+          <t>Home and contact pages complete in staging: NAP, hours, booking link, schema</t>
         </is>
       </c>
       <c r="G51" s="21" t="inlineStr">
@@ -8901,7 +9325,7 @@
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J51" s="21" t="inlineStr">
@@ -8931,12 +9355,12 @@
       </c>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Claim any listing about the practice that is not under your control</t>
+          <t>LocalBusiness and Service schema on every page built so far</t>
         </is>
       </c>
       <c r="G52" s="21" t="inlineStr">
@@ -8951,7 +9375,7 @@
       </c>
       <c r="I52" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J52" s="21" t="inlineStr">
@@ -8981,12 +9405,12 @@
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Verify every corrected listing now shows identical name, address and phone</t>
+          <t>Title tags and meta descriptions for the home and contact pages</t>
         </is>
       </c>
       <c r="G53" s="21" t="inlineStr">
@@ -9031,17 +9455,17 @@
       </c>
       <c r="E54" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Seed the GBP questions section with real questions and answers</t>
+          <t>Correct postal code to L6M 0T9 on the Canadian chamber directories</t>
         </is>
       </c>
       <c r="G54" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H54" s="21" t="inlineStr">
@@ -9051,7 +9475,7 @@
       </c>
       <c r="I54" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J54" s="21" t="inlineStr">
@@ -9081,27 +9505,27 @@
       </c>
       <c r="E55" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Post to GBP every weekday from the content calendar</t>
+          <t>Claim any listing about the practice that is not under your control</t>
         </is>
       </c>
       <c r="G55" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H55" s="21" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I55" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J55" s="21" t="inlineStr">
@@ -9131,12 +9555,12 @@
       </c>
       <c r="E56" s="21" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Compliance pass on the 21 briefs naming Botox or Dysport in client-facing copy</t>
+          <t>Verify every corrected listing now shows identical name, address and phone</t>
         </is>
       </c>
       <c r="G56" s="21" t="inlineStr">
@@ -9181,12 +9605,12 @@
       </c>
       <c r="E57" s="21" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Compliance rules apply to GBP posts too — brief Cleo on what cannot be named</t>
+          <t>Build the healthcare and aesthetics citations, the NPAO listing included</t>
         </is>
       </c>
       <c r="G57" s="21" t="inlineStr">
@@ -9201,7 +9625,7 @@
       </c>
       <c r="I57" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J57" s="21" t="inlineStr">
@@ -9231,12 +9655,12 @@
       </c>
       <c r="E58" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Set up the analytics property ready for launch</t>
+          <t>Check the College of Nurses public register entry is correct as it stands</t>
         </is>
       </c>
       <c r="G58" s="21" t="inlineStr">
@@ -9281,17 +9705,17 @@
       </c>
       <c r="E59" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Google profile</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Send us your current monthly Instagram and Google ad spend</t>
+          <t>Seed the GBP questions section with real questions and answers</t>
         </is>
       </c>
       <c r="G59" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H59" s="21" t="inlineStr">
@@ -9301,7 +9725,7 @@
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J59" s="21" t="inlineStr">
@@ -9318,35 +9742,35 @@
       </c>
       <c r="B60" s="21" t="inlineStr">
         <is>
-          <t>Month 2</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C60" s="21" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="D60" s="22" t="n">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="E60" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Google profile</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Build the treatment pages: lip filler, dermal filler and facial balancing</t>
+          <t>Post to GBP every weekday from the content calendar</t>
         </is>
       </c>
       <c r="G60" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H60" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Daily</t>
         </is>
       </c>
       <c r="I60" s="21" t="inlineStr">
@@ -9368,30 +9792,30 @@
       </c>
       <c r="B61" s="21" t="inlineStr">
         <is>
-          <t>Month 2</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C61" s="21" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="D61" s="22" t="n">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="E61" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Write the copy for those pages and confirm every claim is one you can stand behind</t>
+          <t>Compliance pass on the 21 briefs naming Botox or Dysport in client-facing copy</t>
         </is>
       </c>
       <c r="G61" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H61" s="21" t="inlineStr">
@@ -9418,25 +9842,25 @@
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>Month 2</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C62" s="21" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="D62" s="22" t="n">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="E62" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Title tag, meta description and H1 on every treatment page built</t>
+          <t>Compliance rules apply to GBP posts too — brief Cleo on what cannot be named</t>
         </is>
       </c>
       <c r="G62" s="21" t="inlineStr">
@@ -9468,25 +9892,25 @@
       </c>
       <c r="B63" s="21" t="inlineStr">
         <is>
-          <t>Month 2</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C63" s="21" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="D63" s="22" t="n">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Design and print the QR review card for the treatment room</t>
+          <t>Set up the analytics property ready for launch</t>
         </is>
       </c>
       <c r="G63" s="21" t="inlineStr">
@@ -9518,25 +9942,25 @@
       </c>
       <c r="B64" s="21" t="inlineStr">
         <is>
-          <t>Month 2</t>
+          <t>Month 1</t>
         </is>
       </c>
       <c r="C64" s="21" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="D64" s="22" t="n">
-        <v>46285</v>
+        <v>46278</v>
       </c>
       <c r="E64" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Reply to every new review within two days</t>
+          <t>Send us your current monthly Instagram and Google ad spend</t>
         </is>
       </c>
       <c r="G64" s="21" t="inlineStr">
@@ -9546,12 +9970,12 @@
       </c>
       <c r="H64" s="21" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I64" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J64" s="21" t="inlineStr">
@@ -9581,12 +10005,12 @@
       </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Switch to locally weighted hashtag sets, clear of prescription brand names</t>
+          <t>Build the treatment pages: lip filler, dermal filler and facial balancing</t>
         </is>
       </c>
       <c r="G65" s="21" t="inlineStr">
@@ -9601,7 +10025,7 @@
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J65" s="21" t="inlineStr">
@@ -9631,27 +10055,27 @@
       </c>
       <c r="E66" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Write alt text on every new post</t>
+          <t>Write the copy for those pages and confirm every claim is one you can stand behind</t>
         </is>
       </c>
       <c r="G66" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H66" s="21" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I66" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J66" s="21" t="inlineStr">
@@ -9681,22 +10105,22 @@
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Publish one reel every Wednesday</t>
+          <t>Title tag, meta description and H1 on every treatment page built</t>
         </is>
       </c>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H67" s="21" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
@@ -9723,20 +10147,20 @@
       </c>
       <c r="C68" s="21" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="D68" s="22" t="n">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="E68" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Build the treatment pages: anti-wrinkle injections and skin boosters</t>
+          <t>Build the Canadian directory, maps and social profile citations</t>
         </is>
       </c>
       <c r="G68" s="21" t="inlineStr">
@@ -9751,7 +10175,7 @@
       </c>
       <c r="I68" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J68" s="21" t="inlineStr">
@@ -9773,20 +10197,20 @@
       </c>
       <c r="C69" s="21" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="D69" s="22" t="n">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="E69" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Internal linking pass across every page built so far</t>
+          <t>Design and print the QR review card for the treatment room</t>
         </is>
       </c>
       <c r="G69" s="21" t="inlineStr">
@@ -9823,30 +10247,30 @@
       </c>
       <c r="C70" s="21" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="D70" s="22" t="n">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="E70" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Compress every image and write alt text across the site</t>
+          <t>Reply to every new review within two days</t>
         </is>
       </c>
       <c r="G70" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H70" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="I70" s="21" t="inlineStr">
@@ -9873,11 +10297,11 @@
       </c>
       <c r="C71" s="21" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="D71" s="22" t="n">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="E71" s="21" t="inlineStr">
         <is>
@@ -9886,7 +10310,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Reorganise Highlights by treatment</t>
+          <t>Switch to locally weighted hashtag sets, clear of prescription brand names</t>
         </is>
       </c>
       <c r="G71" s="21" t="inlineStr">
@@ -9923,35 +10347,35 @@
       </c>
       <c r="C72" s="21" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="D72" s="22" t="n">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="E72" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Build the local radius audience, 15km around Oakville</t>
+          <t>Write alt text on every new post</t>
         </is>
       </c>
       <c r="G72" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H72" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Ongoing</t>
         </is>
       </c>
       <c r="I72" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J72" s="21" t="inlineStr">
@@ -9973,30 +10397,30 @@
       </c>
       <c r="C73" s="21" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="D73" s="22" t="n">
-        <v>46292</v>
+        <v>46285</v>
       </c>
       <c r="E73" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Build the 30-day engagement retargeting audience</t>
+          <t>Publish one reel every Wednesday</t>
         </is>
       </c>
       <c r="G73" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H73" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="I73" s="21" t="inlineStr">
@@ -10031,12 +10455,12 @@
       </c>
       <c r="E74" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Check the ask against the review target and adjust it if it is lagging</t>
+          <t>Build the treatment pages: anti-wrinkle injections and skin boosters</t>
         </is>
       </c>
       <c r="G74" s="21" t="inlineStr">
@@ -10046,7 +10470,7 @@
       </c>
       <c r="H74" s="21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I74" s="21" t="inlineStr">
@@ -10073,11 +10497,11 @@
       </c>
       <c r="C75" s="21" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="D75" s="22" t="n">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="E75" s="21" t="inlineStr">
         <is>
@@ -10086,7 +10510,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Build the treatment pages: dermaplaning, electrolysis and Belkyra</t>
+          <t>Internal linking pass across every page built so far</t>
         </is>
       </c>
       <c r="G75" s="21" t="inlineStr">
@@ -10101,7 +10525,7 @@
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J75" s="21" t="inlineStr">
@@ -10123,11 +10547,11 @@
       </c>
       <c r="C76" s="21" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="D76" s="22" t="n">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="E76" s="21" t="inlineStr">
         <is>
@@ -10136,7 +10560,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Build the Oakville and surrounding-area page</t>
+          <t>Compress every image and write alt text across the site</t>
         </is>
       </c>
       <c r="G76" s="21" t="inlineStr">
@@ -10173,20 +10597,20 @@
       </c>
       <c r="C77" s="21" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="D77" s="22" t="n">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="E77" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Mobile speed pass</t>
+          <t>Reorganise Highlights by treatment</t>
         </is>
       </c>
       <c r="G77" s="21" t="inlineStr">
@@ -10223,11 +10647,11 @@
       </c>
       <c r="C78" s="21" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="D78" s="22" t="n">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="E78" s="21" t="inlineStr">
         <is>
@@ -10236,12 +10660,12 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Export the patient list from the booking system for the lookalike audience</t>
+          <t>Build the local radius audience, 15km around Oakville</t>
         </is>
       </c>
       <c r="G78" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H78" s="21" t="inlineStr">
@@ -10251,7 +10675,7 @@
       </c>
       <c r="I78" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J78" s="21" t="inlineStr">
@@ -10273,11 +10697,11 @@
       </c>
       <c r="C79" s="21" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="D79" s="22" t="n">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="E79" s="21" t="inlineStr">
         <is>
@@ -10286,7 +10710,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Build the lookalike audience</t>
+          <t>Build the 30-day engagement retargeting audience</t>
         </is>
       </c>
       <c r="G79" s="21" t="inlineStr">
@@ -10301,7 +10725,7 @@
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J79" s="21" t="inlineStr">
@@ -10323,20 +10747,20 @@
       </c>
       <c r="C80" s="21" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="D80" s="22" t="n">
-        <v>46299</v>
+        <v>46292</v>
       </c>
       <c r="E80" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Launch three or four ad creatives pulled from existing carousels</t>
+          <t>Check the ask against the review target and adjust it if it is lagging</t>
         </is>
       </c>
       <c r="G80" s="21" t="inlineStr">
@@ -10346,7 +10770,7 @@
       </c>
       <c r="H80" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I80" s="21" t="inlineStr">
@@ -10373,11 +10797,11 @@
       </c>
       <c r="C81" s="21" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="D81" s="22" t="n">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="E81" s="21" t="inlineStr">
         <is>
@@ -10386,12 +10810,12 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Final content and compliance review of every page before launch</t>
+          <t>Build the treatment pages: dermaplaning, electrolysis and Belkyra</t>
         </is>
       </c>
       <c r="G81" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H81" s="21" t="inlineStr">
@@ -10423,11 +10847,11 @@
       </c>
       <c r="C82" s="21" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="D82" s="22" t="n">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
@@ -10436,7 +10860,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>LAUNCH: site live, Search Console verified, sitemap submitted, analytics running</t>
+          <t>Build the Oakville and surrounding-area page</t>
         </is>
       </c>
       <c r="G82" s="21" t="inlineStr">
@@ -10451,7 +10875,7 @@
       </c>
       <c r="I82" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J82" s="21" t="inlineStr">
@@ -10473,11 +10897,11 @@
       </c>
       <c r="C83" s="21" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="D83" s="22" t="n">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="E83" s="21" t="inlineStr">
         <is>
@@ -10486,7 +10910,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Repoint the GBP website field at the live site</t>
+          <t>Mobile speed pass</t>
         </is>
       </c>
       <c r="G83" s="21" t="inlineStr">
@@ -10501,7 +10925,7 @@
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J83" s="21" t="inlineStr">
@@ -10523,25 +10947,25 @@
       </c>
       <c r="C84" s="21" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="D84" s="22" t="n">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="E84" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Update every directory listing to the new website URL</t>
+          <t>Export the patient list from the booking system for the lookalike audience</t>
         </is>
       </c>
       <c r="G84" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H84" s="21" t="inlineStr">
@@ -10573,20 +10997,20 @@
       </c>
       <c r="C85" s="21" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="D85" s="22" t="n">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="E85" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Update the link in bio to the live site</t>
+          <t>Build the lookalike audience</t>
         </is>
       </c>
       <c r="G85" s="21" t="inlineStr">
@@ -10601,7 +11025,7 @@
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J85" s="21" t="inlineStr">
@@ -10623,20 +11047,20 @@
       </c>
       <c r="C86" s="21" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="D86" s="22" t="n">
-        <v>46306</v>
+        <v>46299</v>
       </c>
       <c r="E86" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Confirm Search Console and analytics are both recording on the live domain</t>
+          <t>Launch three or four ad creatives pulled from existing carousels</t>
         </is>
       </c>
       <c r="G86" s="21" t="inlineStr">
@@ -10681,22 +11105,22 @@
       </c>
       <c r="E87" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
+          <t>Final content and compliance review of every page before launch</t>
         </is>
       </c>
       <c r="G87" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H87" s="21" t="inlineStr">
         <is>
-          <t>Fortnightly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
@@ -10718,16 +11142,16 @@
       </c>
       <c r="B88" s="21" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C88" s="21" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="D88" s="22" t="n">
-        <v>46313</v>
+        <v>46306</v>
       </c>
       <c r="E88" s="21" t="inlineStr">
         <is>
@@ -10736,7 +11160,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Confirm every page is indexed in Search Console and fix what is not</t>
+          <t>LAUNCH: site live, Search Console verified, sitemap submitted, analytics running</t>
         </is>
       </c>
       <c r="G88" s="21" t="inlineStr">
@@ -10768,16 +11192,16 @@
       </c>
       <c r="B89" s="21" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C89" s="21" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="D89" s="22" t="n">
-        <v>46313</v>
+        <v>46306</v>
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
@@ -10786,7 +11210,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>On-page pass on the home page: title, H1, opening copy, internal links</t>
+          <t>Repoint the GBP website field at the live site</t>
         </is>
       </c>
       <c r="G89" s="21" t="inlineStr">
@@ -10818,25 +11242,25 @@
       </c>
       <c r="B90" s="21" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C90" s="21" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="D90" s="22" t="n">
-        <v>46313</v>
+        <v>46306</v>
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>Local links</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Submit to the Oakville business directories</t>
+          <t>Update every directory listing to the new website URL</t>
         </is>
       </c>
       <c r="G90" s="21" t="inlineStr">
@@ -10868,30 +11292,30 @@
       </c>
       <c r="B91" s="21" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C91" s="21" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="D91" s="22" t="n">
-        <v>46313</v>
+        <v>46306</v>
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>Local links</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Ask Allure about a cross-link between the two businesses</t>
+          <t>Update every citation built before launch from the booking link to the live site URL</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H91" s="21" t="inlineStr">
@@ -10901,7 +11325,7 @@
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J91" s="21" t="inlineStr">
@@ -10918,25 +11342,25 @@
       </c>
       <c r="B92" s="21" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C92" s="21" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="D92" s="22" t="n">
-        <v>46313</v>
+        <v>46306</v>
       </c>
       <c r="E92" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>First post-launch read on Search Console impressions and queries</t>
+          <t>Update the link in bio to the live site</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
@@ -10951,7 +11375,7 @@
       </c>
       <c r="I92" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J92" s="21" t="inlineStr">
@@ -10968,25 +11392,25 @@
       </c>
       <c r="B93" s="21" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C93" s="21" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="D93" s="22" t="n">
-        <v>46320</v>
+        <v>46306</v>
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>On-page pass on the four highest-intent treatment pages</t>
+          <t>Confirm Search Console and analytics are both recording on the live domain</t>
         </is>
       </c>
       <c r="G93" s="21" t="inlineStr">
@@ -11018,25 +11442,25 @@
       </c>
       <c r="B94" s="21" t="inlineStr">
         <is>
-          <t>Month 3</t>
+          <t>Month 2</t>
         </is>
       </c>
       <c r="C94" s="21" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="D94" s="22" t="n">
-        <v>46320</v>
+        <v>46306</v>
       </c>
       <c r="E94" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Add FAQ blocks with FAQ schema to every treatment page</t>
+          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
         </is>
       </c>
       <c r="G94" s="21" t="inlineStr">
@@ -11046,12 +11470,12 @@
       </c>
       <c r="H94" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Fortnightly</t>
         </is>
       </c>
       <c r="I94" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J94" s="21" t="inlineStr">
@@ -11073,20 +11497,20 @@
       </c>
       <c r="C95" s="21" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="D95" s="22" t="n">
-        <v>46320</v>
+        <v>46313</v>
       </c>
       <c r="E95" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Write the first question-intent article and link it to its treatment page</t>
+          <t>Confirm every page is indexed in Search Console and fix what is not</t>
         </is>
       </c>
       <c r="G95" s="21" t="inlineStr">
@@ -11101,7 +11525,7 @@
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J95" s="21" t="inlineStr">
@@ -11123,20 +11547,20 @@
       </c>
       <c r="C96" s="21" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="D96" s="22" t="n">
-        <v>46320</v>
+        <v>46313</v>
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>Local links</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Approach Halton-area partners for mentions and links</t>
+          <t>On-page pass on the home page: title, H1, opening copy, internal links</t>
         </is>
       </c>
       <c r="G96" s="21" t="inlineStr">
@@ -11151,7 +11575,7 @@
       </c>
       <c r="I96" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J96" s="21" t="inlineStr">
@@ -11173,20 +11597,20 @@
       </c>
       <c r="C97" s="21" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="D97" s="22" t="n">
-        <v>46320</v>
+        <v>46313</v>
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Local links</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Add the weight-loss service entry to GBP ahead of the launch</t>
+          <t>Submit to the Oakville business directories</t>
         </is>
       </c>
       <c r="G97" s="21" t="inlineStr">
@@ -11223,25 +11647,25 @@
       </c>
       <c r="C98" s="21" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="D98" s="22" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="E98" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Local links</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Fix whatever Search Console flags: coverage, mobile usability, core web vitals</t>
+          <t>Ask Allure about a cross-link between the two businesses</t>
         </is>
       </c>
       <c r="G98" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H98" s="21" t="inlineStr">
@@ -11251,7 +11675,7 @@
       </c>
       <c r="I98" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J98" s="21" t="inlineStr">
@@ -11273,20 +11697,20 @@
       </c>
       <c r="C99" s="21" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="D99" s="22" t="n">
-        <v>46327</v>
+        <v>46313</v>
       </c>
       <c r="E99" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Write the second question-intent article</t>
+          <t>First post-launch read on Search Console impressions and queries</t>
         </is>
       </c>
       <c r="G99" s="21" t="inlineStr">
@@ -11323,20 +11747,20 @@
       </c>
       <c r="C100" s="21" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="D100" s="22" t="n">
-        <v>46327</v>
+        <v>46320</v>
       </c>
       <c r="E100" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
+          <t>On-page pass on the four highest-intent treatment pages</t>
         </is>
       </c>
       <c r="G100" s="21" t="inlineStr">
@@ -11346,7 +11770,7 @@
       </c>
       <c r="H100" s="21" t="inlineStr">
         <is>
-          <t>Fortnightly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I100" s="21" t="inlineStr">
@@ -11373,20 +11797,20 @@
       </c>
       <c r="C101" s="21" t="inlineStr">
         <is>
-          <t>W11</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="D101" s="22" t="n">
-        <v>46327</v>
+        <v>46320</v>
       </c>
       <c r="E101" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>Check the ask conversion rate and rewrite the message if it is under 30 per cent</t>
+          <t>Add FAQ blocks with FAQ schema to every treatment page</t>
         </is>
       </c>
       <c r="G101" s="21" t="inlineStr">
@@ -11401,7 +11825,7 @@
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J101" s="21" t="inlineStr">
@@ -11423,20 +11847,20 @@
       </c>
       <c r="C102" s="21" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="D102" s="22" t="n">
-        <v>46334</v>
+        <v>46320</v>
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>Month three review: every number against the week-one baseline</t>
+          <t>Write the first question-intent article and link it to its treatment page</t>
         </is>
       </c>
       <c r="G102" s="21" t="inlineStr">
@@ -11446,12 +11870,12 @@
       </c>
       <c r="H102" s="21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I102" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J102" s="21" t="inlineStr">
@@ -11473,20 +11897,20 @@
       </c>
       <c r="C103" s="21" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="D103" s="22" t="n">
-        <v>46334</v>
+        <v>46320</v>
       </c>
       <c r="E103" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Local links</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Rank check on the map pack terms and the page terms</t>
+          <t>Approach Halton-area partners for mentions and links</t>
         </is>
       </c>
       <c r="G103" s="21" t="inlineStr">
@@ -11496,12 +11920,12 @@
       </c>
       <c r="H103" s="21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J103" s="21" t="inlineStr">
@@ -11523,20 +11947,20 @@
       </c>
       <c r="C104" s="21" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W10</t>
         </is>
       </c>
       <c r="D104" s="22" t="n">
-        <v>46334</v>
+        <v>46320</v>
       </c>
       <c r="E104" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Google profile</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Write the third question-intent article</t>
+          <t>Add the weight-loss service entry to GBP ahead of the launch</t>
         </is>
       </c>
       <c r="G104" s="21" t="inlineStr">
@@ -11573,20 +11997,20 @@
       </c>
       <c r="C105" s="21" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="D105" s="22" t="n">
-        <v>46334</v>
+        <v>46327</v>
       </c>
       <c r="E105" s="21" t="inlineStr">
         <is>
-          <t>Local links</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Chase every unanswered link approach</t>
+          <t>Fix whatever Search Console flags: coverage, mobile usability, core web vitals</t>
         </is>
       </c>
       <c r="G105" s="21" t="inlineStr">
@@ -11601,7 +12025,7 @@
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J105" s="21" t="inlineStr">
@@ -11618,25 +12042,25 @@
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C106" s="21" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="D106" s="22" t="n">
-        <v>46341</v>
+        <v>46327</v>
       </c>
       <c r="E106" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Build the weight-loss pre-launch page</t>
+          <t>Write the second question-intent article</t>
         </is>
       </c>
       <c r="G106" s="21" t="inlineStr">
@@ -11668,25 +12092,25 @@
       </c>
       <c r="B107" s="21" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C107" s="21" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="D107" s="22" t="n">
-        <v>46341</v>
+        <v>46327</v>
       </c>
       <c r="E107" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Write the fourth article from the questions you get asked in consults</t>
+          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
         </is>
       </c>
       <c r="G107" s="21" t="inlineStr">
@@ -11696,12 +12120,12 @@
       </c>
       <c r="H107" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Fortnightly</t>
         </is>
       </c>
       <c r="I107" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J107" s="21" t="inlineStr">
@@ -11718,25 +12142,25 @@
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C108" s="21" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="D108" s="22" t="n">
-        <v>46341</v>
+        <v>46327</v>
       </c>
       <c r="E108" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Review which posts drove profile visits and rebalance the calendar</t>
+          <t>Check the ask conversion rate and rewrite the message if it is under 30 per cent</t>
         </is>
       </c>
       <c r="G108" s="21" t="inlineStr">
@@ -11746,12 +12170,12 @@
       </c>
       <c r="H108" s="21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I108" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J108" s="21" t="inlineStr">
@@ -11768,40 +12192,40 @@
       </c>
       <c r="B109" s="21" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C109" s="21" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="D109" s="22" t="n">
-        <v>46341</v>
+        <v>46334</v>
       </c>
       <c r="E109" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Refresh the GBP photo set with new room and result photos</t>
+          <t>Month three review: every number against the week-one baseline</t>
         </is>
       </c>
       <c r="G109" s="21" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H109" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J109" s="21" t="inlineStr">
@@ -11818,25 +12242,25 @@
       </c>
       <c r="B110" s="21" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C110" s="21" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="D110" s="22" t="n">
-        <v>46348</v>
+        <v>46334</v>
       </c>
       <c r="E110" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Expand the thin treatment pages: pricing ranges, aftercare, who it is not for</t>
+          <t>Rank check on the map pack terms and the page terms</t>
         </is>
       </c>
       <c r="G110" s="21" t="inlineStr">
@@ -11846,7 +12270,7 @@
       </c>
       <c r="H110" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I110" s="21" t="inlineStr">
@@ -11868,30 +12292,30 @@
       </c>
       <c r="B111" s="21" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C111" s="21" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="D111" s="22" t="n">
-        <v>46348</v>
+        <v>46334</v>
       </c>
       <c r="E111" s="21" t="inlineStr">
         <is>
-          <t>Local links</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Sponsor or join one Oakville community listing or event</t>
+          <t>Write the third question-intent article</t>
         </is>
       </c>
       <c r="G111" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H111" s="21" t="inlineStr">
@@ -11918,25 +12342,25 @@
       </c>
       <c r="B112" s="21" t="inlineStr">
         <is>
-          <t>Month 4</t>
+          <t>Month 3</t>
         </is>
       </c>
       <c r="C112" s="21" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="D112" s="22" t="n">
-        <v>46348</v>
+        <v>46334</v>
       </c>
       <c r="E112" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Local links</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
+          <t>Chase every unanswered link approach</t>
         </is>
       </c>
       <c r="G112" s="21" t="inlineStr">
@@ -11946,12 +12370,12 @@
       </c>
       <c r="H112" s="21" t="inlineStr">
         <is>
-          <t>Fortnightly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I112" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J112" s="21" t="inlineStr">
@@ -11973,20 +12397,20 @@
       </c>
       <c r="C113" s="21" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="D113" s="22" t="n">
-        <v>46348</v>
+        <v>46341</v>
       </c>
       <c r="E113" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Write the fifth article</t>
+          <t>Build the weight-loss pre-launch page</t>
         </is>
       </c>
       <c r="G113" s="21" t="inlineStr">
@@ -12023,20 +12447,20 @@
       </c>
       <c r="C114" s="21" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="D114" s="22" t="n">
-        <v>46355</v>
+        <v>46341</v>
       </c>
       <c r="E114" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Add a before-and-after gallery page using consent-cleared photos only</t>
+          <t>Write the fourth article from the questions you get asked in consults</t>
         </is>
       </c>
       <c r="G114" s="21" t="inlineStr">
@@ -12073,20 +12497,20 @@
       </c>
       <c r="C115" s="21" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="D115" s="22" t="n">
-        <v>46355</v>
+        <v>46341</v>
       </c>
       <c r="E115" s="21" t="inlineStr">
         <is>
-          <t>Compliance</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Compliance pass on the gallery page before it goes live</t>
+          <t>Review which posts drove profile visits and rebalance the calendar</t>
         </is>
       </c>
       <c r="G115" s="21" t="inlineStr">
@@ -12096,12 +12520,12 @@
       </c>
       <c r="H115" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J115" s="21" t="inlineStr">
@@ -12123,11 +12547,11 @@
       </c>
       <c r="C116" s="21" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W13</t>
         </is>
       </c>
       <c r="D116" s="22" t="n">
-        <v>46355</v>
+        <v>46341</v>
       </c>
       <c r="E116" s="21" t="inlineStr">
         <is>
@@ -12136,12 +12560,12 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Post the December holiday hours to GBP</t>
+          <t>Refresh the GBP photo set with new room and result photos</t>
         </is>
       </c>
       <c r="G116" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Both</t>
         </is>
       </c>
       <c r="H116" s="21" t="inlineStr">
@@ -12173,25 +12597,25 @@
       </c>
       <c r="C117" s="21" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="D117" s="22" t="n">
-        <v>46355</v>
+        <v>46348</v>
       </c>
       <c r="E117" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Holiday review push: ask every patient seen in November</t>
+          <t>Expand the thin treatment pages: pricing ranges, aftercare, who it is not for</t>
         </is>
       </c>
       <c r="G117" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H117" s="21" t="inlineStr">
@@ -12223,35 +12647,35 @@
       </c>
       <c r="C118" s="21" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="D118" s="22" t="n">
-        <v>46362</v>
+        <v>46348</v>
       </c>
       <c r="E118" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Local links</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Month four review: compare Search Console queries month on month</t>
+          <t>Sponsor or join one Oakville community listing or event</t>
         </is>
       </c>
       <c r="G118" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H118" s="21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I118" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J118" s="21" t="inlineStr">
@@ -12273,20 +12697,20 @@
       </c>
       <c r="C119" s="21" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="D119" s="22" t="n">
-        <v>46362</v>
+        <v>46348</v>
       </c>
       <c r="E119" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Internal linking pass now that the articles exist</t>
+          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
         </is>
       </c>
       <c r="G119" s="21" t="inlineStr">
@@ -12296,12 +12720,12 @@
       </c>
       <c r="H119" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Fortnightly</t>
         </is>
       </c>
       <c r="I119" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J119" s="21" t="inlineStr">
@@ -12323,11 +12747,11 @@
       </c>
       <c r="C120" s="21" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="D120" s="22" t="n">
-        <v>46362</v>
+        <v>46348</v>
       </c>
       <c r="E120" s="21" t="inlineStr">
         <is>
@@ -12336,7 +12760,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Write the sixth article</t>
+          <t>Write the fifth article</t>
         </is>
       </c>
       <c r="G120" s="21" t="inlineStr">
@@ -12368,25 +12792,25 @@
       </c>
       <c r="B121" s="21" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C121" s="21" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="D121" s="22" t="n">
-        <v>46369</v>
+        <v>46355</v>
       </c>
       <c r="E121" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Set the holiday opening hours on GBP for December and January</t>
+          <t>Add a before-and-after gallery page using consent-cleared photos only</t>
         </is>
       </c>
       <c r="G121" s="21" t="inlineStr">
@@ -12401,7 +12825,7 @@
       </c>
       <c r="I121" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J121" s="21" t="inlineStr">
@@ -12418,25 +12842,25 @@
       </c>
       <c r="B122" s="21" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C122" s="21" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="D122" s="22" t="n">
-        <v>46369</v>
+        <v>46355</v>
       </c>
       <c r="E122" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Compliance</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Plan the December gift-card and holiday content</t>
+          <t>Compliance pass on the gallery page before it goes live</t>
         </is>
       </c>
       <c r="G122" s="21" t="inlineStr">
@@ -12451,7 +12875,7 @@
       </c>
       <c r="I122" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J122" s="21" t="inlineStr">
@@ -12468,25 +12892,25 @@
       </c>
       <c r="B123" s="21" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="D123" s="22" t="n">
-        <v>46369</v>
+        <v>46355</v>
       </c>
       <c r="E123" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Google profile</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Add a gift-card or holiday offer block to the home page</t>
+          <t>Post the December holiday hours to GBP</t>
         </is>
       </c>
       <c r="G123" s="21" t="inlineStr">
@@ -12518,35 +12942,35 @@
       </c>
       <c r="B124" s="21" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="D124" s="22" t="n">
-        <v>46376</v>
+        <v>46355</v>
       </c>
       <c r="E124" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Holiday campaign: reallocate budget to the gift-card creative</t>
+          <t>Holiday review push: ask every patient seen in November</t>
         </is>
       </c>
       <c r="G124" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H124" s="21" t="inlineStr">
         <is>
-          <t>Fortnightly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I124" s="21" t="inlineStr">
@@ -12568,25 +12992,25 @@
       </c>
       <c r="B125" s="21" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="D125" s="22" t="n">
-        <v>46376</v>
+        <v>46362</v>
       </c>
       <c r="E125" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Write the seventh article</t>
+          <t>Month four review: compare Search Console queries month on month</t>
         </is>
       </c>
       <c r="G125" s="21" t="inlineStr">
@@ -12596,12 +13020,12 @@
       </c>
       <c r="H125" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I125" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J125" s="21" t="inlineStr">
@@ -12618,25 +13042,25 @@
       </c>
       <c r="B126" s="21" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="D126" s="22" t="n">
-        <v>46376</v>
+        <v>46362</v>
       </c>
       <c r="E126" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Quarterly citation audit: confirm the NAP is still identical everywhere</t>
+          <t>Internal linking pass now that the articles exist</t>
         </is>
       </c>
       <c r="G126" s="21" t="inlineStr">
@@ -12668,30 +13092,30 @@
       </c>
       <c r="B127" s="21" t="inlineStr">
         <is>
-          <t>Month 5</t>
+          <t>Month 4</t>
         </is>
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="D127" s="22" t="n">
-        <v>46383</v>
+        <v>46362</v>
       </c>
       <c r="E127" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Reduced holiday cadence: stories only, one reel, but keep GBP posting daily</t>
+          <t>Write the sixth article</t>
         </is>
       </c>
       <c r="G127" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H127" s="21" t="inlineStr">
@@ -12723,11 +13147,11 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="D128" s="22" t="n">
-        <v>46383</v>
+        <v>46369</v>
       </c>
       <c r="E128" s="21" t="inlineStr">
         <is>
@@ -12736,7 +13160,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Confirm the holiday hours showing on Google are actually correct</t>
+          <t>Set the holiday opening hours on GBP for December and January</t>
         </is>
       </c>
       <c r="G128" s="21" t="inlineStr">
@@ -12773,20 +13197,20 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="D129" s="22" t="n">
-        <v>46390</v>
+        <v>46369</v>
       </c>
       <c r="E129" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Year-end read: reviews, map pack positions, sessions and bookings</t>
+          <t>Plan the December gift-card and holiday content</t>
         </is>
       </c>
       <c r="G129" s="21" t="inlineStr">
@@ -12796,12 +13220,12 @@
       </c>
       <c r="H129" s="21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I129" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J129" s="21" t="inlineStr">
@@ -12823,20 +13247,20 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="D130" s="22" t="n">
-        <v>46390</v>
+        <v>46369</v>
       </c>
       <c r="E130" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Plan the January content calendar</t>
+          <t>Add a gift-card or holiday offer block to the home page</t>
         </is>
       </c>
       <c r="G130" s="21" t="inlineStr">
@@ -12873,20 +13297,20 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="D131" s="22" t="n">
-        <v>46397</v>
+        <v>46376</v>
       </c>
       <c r="E131" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>January on-page sprint: refresh every title tag and meta description</t>
+          <t>Holiday campaign: reallocate budget to the gift-card creative</t>
         </is>
       </c>
       <c r="G131" s="21" t="inlineStr">
@@ -12896,7 +13320,7 @@
       </c>
       <c r="H131" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Fortnightly</t>
         </is>
       </c>
       <c r="I131" s="21" t="inlineStr">
@@ -12923,25 +13347,25 @@
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="D132" s="22" t="n">
-        <v>46397</v>
+        <v>46376</v>
       </c>
       <c r="E132" s="21" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Back to full cadence with new-year treatment content</t>
+          <t>Write the seventh article</t>
         </is>
       </c>
       <c r="G132" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H132" s="21" t="inlineStr">
@@ -12951,7 +13375,7 @@
       </c>
       <c r="I132" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J132" s="21" t="inlineStr">
@@ -12973,25 +13397,25 @@
       </c>
       <c r="C133" s="21" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="D133" s="22" t="n">
-        <v>46397</v>
+        <v>46376</v>
       </c>
       <c r="E133" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Citations</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>New-year review push</t>
+          <t>Quarterly citation audit across both the Citations and Local Citations tabs</t>
         </is>
       </c>
       <c r="G133" s="21" t="inlineStr">
         <is>
-          <t>Cleo</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="H133" s="21" t="inlineStr">
@@ -13001,7 +13425,7 @@
       </c>
       <c r="I133" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J133" s="21" t="inlineStr">
@@ -13023,35 +13447,35 @@
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="D134" s="22" t="n">
-        <v>46397</v>
+        <v>46383</v>
       </c>
       <c r="E134" s="21" t="inlineStr">
         <is>
-          <t>Ads</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Relaunch the standard campaign set after the holiday creative</t>
+          <t>Reduced holiday cadence: stories only, one reel, but keep GBP posting daily</t>
         </is>
       </c>
       <c r="G134" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H134" s="21" t="inlineStr">
         <is>
-          <t>Fortnightly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I134" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J134" s="21" t="inlineStr">
@@ -13068,25 +13492,25 @@
       </c>
       <c r="B135" s="21" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C135" s="21" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
-        <v>46404</v>
+        <v>46383</v>
       </c>
       <c r="E135" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Google profile</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Build the full weight-loss treatment page now the service is live</t>
+          <t>Confirm the holiday hours showing on Google are actually correct</t>
         </is>
       </c>
       <c r="G135" s="21" t="inlineStr">
@@ -13118,25 +13542,25 @@
       </c>
       <c r="B136" s="21" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C136" s="21" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="D136" s="22" t="n">
-        <v>46404</v>
+        <v>46390</v>
       </c>
       <c r="E136" s="21" t="inlineStr">
         <is>
-          <t>Content</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Write the eighth article</t>
+          <t>Year-end read: reviews, map pack positions, sessions and bookings</t>
         </is>
       </c>
       <c r="G136" s="21" t="inlineStr">
@@ -13146,12 +13570,12 @@
       </c>
       <c r="H136" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I136" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J136" s="21" t="inlineStr">
@@ -13168,25 +13592,25 @@
       </c>
       <c r="B137" s="21" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C137" s="21" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="D137" s="22" t="n">
-        <v>46404</v>
+        <v>46390</v>
       </c>
       <c r="E137" s="21" t="inlineStr">
         <is>
-          <t>Local links</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Second round of local link approaches</t>
+          <t>Plan the January content calendar</t>
         </is>
       </c>
       <c r="G137" s="21" t="inlineStr">
@@ -13218,25 +13642,25 @@
       </c>
       <c r="B138" s="21" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C138" s="21" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="D138" s="22" t="n">
-        <v>46411</v>
+        <v>46397</v>
       </c>
       <c r="E138" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Full query review: find every term you rank between 5 and 15 for</t>
+          <t>January on-page sprint: refresh every title tag and meta description</t>
         </is>
       </c>
       <c r="G138" s="21" t="inlineStr">
@@ -13268,30 +13692,30 @@
       </c>
       <c r="B139" s="21" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C139" s="21" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="D139" s="22" t="n">
-        <v>46411</v>
+        <v>46397</v>
       </c>
       <c r="E139" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Optimise the pages behind those near-miss terms</t>
+          <t>Back to full cadence with new-year treatment content</t>
         </is>
       </c>
       <c r="G139" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H139" s="21" t="inlineStr">
@@ -13318,30 +13742,30 @@
       </c>
       <c r="B140" s="21" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C140" s="21" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="D140" s="22" t="n">
-        <v>46411</v>
+        <v>46397</v>
       </c>
       <c r="E140" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Content refresh on the three lowest-performing pages</t>
+          <t>New-year review push</t>
         </is>
       </c>
       <c r="G140" s="21" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Cleo</t>
         </is>
       </c>
       <c r="H140" s="21" t="inlineStr">
@@ -13351,7 +13775,7 @@
       </c>
       <c r="I140" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J140" s="21" t="inlineStr">
@@ -13368,16 +13792,16 @@
       </c>
       <c r="B141" s="21" t="inlineStr">
         <is>
-          <t>Month 6</t>
+          <t>Month 5</t>
         </is>
       </c>
       <c r="C141" s="21" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="D141" s="22" t="n">
-        <v>46418</v>
+        <v>46397</v>
       </c>
       <c r="E141" s="21" t="inlineStr">
         <is>
@@ -13386,7 +13810,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
+          <t>Relaunch the standard campaign set after the holiday creative</t>
         </is>
       </c>
       <c r="G141" s="21" t="inlineStr">
@@ -13423,20 +13847,20 @@
       </c>
       <c r="C142" s="21" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="D142" s="22" t="n">
-        <v>46418</v>
+        <v>46404</v>
       </c>
       <c r="E142" s="21" t="inlineStr">
         <is>
-          <t>Reviews</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Check the review count against the six-month target</t>
+          <t>Build the full weight-loss treatment page now the service is live</t>
         </is>
       </c>
       <c r="G142" s="21" t="inlineStr">
@@ -13446,7 +13870,7 @@
       </c>
       <c r="H142" s="21" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I142" s="21" t="inlineStr">
@@ -13473,20 +13897,20 @@
       </c>
       <c r="C143" s="21" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="D143" s="22" t="n">
-        <v>46418</v>
+        <v>46404</v>
       </c>
       <c r="E143" s="21" t="inlineStr">
         <is>
-          <t>Google profile</t>
+          <t>Content</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Refresh the GBP services list and the questions section</t>
+          <t>Write the eighth article</t>
         </is>
       </c>
       <c r="G143" s="21" t="inlineStr">
@@ -13523,20 +13947,20 @@
       </c>
       <c r="C144" s="21" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="D144" s="22" t="n">
-        <v>46425</v>
+        <v>46404</v>
       </c>
       <c r="E144" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Local links</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Full review of every number against the week-one baseline</t>
+          <t>Second round of local link approaches</t>
         </is>
       </c>
       <c r="G144" s="21" t="inlineStr">
@@ -13551,7 +13975,7 @@
       </c>
       <c r="I144" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J144" s="21" t="inlineStr">
@@ -13573,20 +13997,20 @@
       </c>
       <c r="C145" s="21" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="D145" s="22" t="n">
-        <v>46425</v>
+        <v>46411</v>
       </c>
       <c r="E145" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Technical audit: speed, schema, broken links, redirects</t>
+          <t>Full query review: find every term you rank between 5 and 15 for</t>
         </is>
       </c>
       <c r="G145" s="21" t="inlineStr">
@@ -13623,20 +14047,20 @@
       </c>
       <c r="C146" s="21" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="D146" s="22" t="n">
-        <v>46425</v>
+        <v>46411</v>
       </c>
       <c r="E146" s="21" t="inlineStr">
         <is>
-          <t>Citations</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Final citation audit for the engagement</t>
+          <t>Optimise the pages behind those near-miss terms</t>
         </is>
       </c>
       <c r="G146" s="21" t="inlineStr">
@@ -13651,7 +14075,7 @@
       </c>
       <c r="I146" s="21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J146" s="21" t="inlineStr">
@@ -13673,20 +14097,20 @@
       </c>
       <c r="C147" s="21" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="D147" s="22" t="n">
-        <v>46432</v>
+        <v>46411</v>
       </c>
       <c r="E147" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Write the six-month report</t>
+          <t>Content refresh on the three lowest-performing pages</t>
         </is>
       </c>
       <c r="G147" s="21" t="inlineStr">
@@ -13701,7 +14125,7 @@
       </c>
       <c r="I147" s="21" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J147" s="21" t="inlineStr">
@@ -13723,20 +14147,20 @@
       </c>
       <c r="C148" s="21" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="D148" s="22" t="n">
-        <v>46432</v>
+        <v>46418</v>
       </c>
       <c r="E148" s="21" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Ads</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>Write the recommendation for the next six months</t>
+          <t>Fortnightly ad review: kill anything below average cost per DM, reallocate</t>
         </is>
       </c>
       <c r="G148" s="21" t="inlineStr">
@@ -13746,7 +14170,7 @@
       </c>
       <c r="H148" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Fortnightly</t>
         </is>
       </c>
       <c r="I148" s="21" t="inlineStr">
@@ -13773,20 +14197,20 @@
       </c>
       <c r="C149" s="21" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="D149" s="22" t="n">
-        <v>46432</v>
+        <v>46418</v>
       </c>
       <c r="E149" s="21" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Reviews</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Hand over the site documentation and every login</t>
+          <t>Check the review count against the six-month target</t>
         </is>
       </c>
       <c r="G149" s="21" t="inlineStr">
@@ -13796,7 +14220,7 @@
       </c>
       <c r="H149" s="21" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I149" s="21" t="inlineStr">
@@ -13812,9 +14236,359 @@
       <c r="K149" s="22" t="n"/>
       <c r="L149" s="4" t="n"/>
     </row>
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" s="21" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="21" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="C150" s="21" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="n">
+        <v>46418</v>
+      </c>
+      <c r="E150" s="21" t="inlineStr">
+        <is>
+          <t>Google profile</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Refresh the GBP services list and the questions section</t>
+        </is>
+      </c>
+      <c r="G150" s="21" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="H150" s="21" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I150" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J150" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K150" s="22" t="n"/>
+      <c r="L150" s="4" t="n"/>
+    </row>
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="21" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="C151" s="21" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="D151" s="22" t="n">
+        <v>46425</v>
+      </c>
+      <c r="E151" s="21" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>Full review of every number against the week-one baseline</t>
+        </is>
+      </c>
+      <c r="G151" s="21" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="H151" s="21" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I151" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J151" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K151" s="22" t="n"/>
+      <c r="L151" s="4" t="n"/>
+    </row>
+    <row r="152" ht="15" customHeight="1">
+      <c r="A152" s="21" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="21" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="C152" s="21" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="n">
+        <v>46425</v>
+      </c>
+      <c r="E152" s="21" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>Technical audit: speed, schema, broken links, redirects</t>
+        </is>
+      </c>
+      <c r="G152" s="21" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="H152" s="21" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I152" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J152" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K152" s="22" t="n"/>
+      <c r="L152" s="4" t="n"/>
+    </row>
+    <row r="153" ht="15" customHeight="1">
+      <c r="A153" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="21" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="C153" s="21" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="n">
+        <v>46425</v>
+      </c>
+      <c r="E153" s="21" t="inlineStr">
+        <is>
+          <t>Citations</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
+        <is>
+          <t>Final citation audit for the engagement</t>
+        </is>
+      </c>
+      <c r="G153" s="21" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="H153" s="21" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I153" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J153" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K153" s="22" t="n"/>
+      <c r="L153" s="4" t="n"/>
+    </row>
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" s="21" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="21" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="C154" s="21" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="n">
+        <v>46432</v>
+      </c>
+      <c r="E154" s="21" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>Write the six-month report</t>
+        </is>
+      </c>
+      <c r="G154" s="21" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="H154" s="21" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I154" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J154" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K154" s="22" t="n"/>
+      <c r="L154" s="4" t="n"/>
+    </row>
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="21" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="21" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="C155" s="21" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="D155" s="22" t="n">
+        <v>46432</v>
+      </c>
+      <c r="E155" s="21" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="F155" s="4" t="inlineStr">
+        <is>
+          <t>Write the recommendation for the next six months</t>
+        </is>
+      </c>
+      <c r="G155" s="21" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="H155" s="21" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I155" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J155" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K155" s="22" t="n"/>
+      <c r="L155" s="4" t="n"/>
+    </row>
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="21" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="21" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="C156" s="21" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="n">
+        <v>46432</v>
+      </c>
+      <c r="E156" s="21" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Hand over the site documentation and every login</t>
+        </is>
+      </c>
+      <c r="G156" s="21" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="H156" s="21" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I156" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J156" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="K156" s="22" t="n"/>
+      <c r="L156" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L149"/>
-  <conditionalFormatting sqref="A2:L149">
+  <autoFilter ref="A1:L156"/>
+  <conditionalFormatting sqref="A2:L156">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$J2="Done"</formula>
     </cfRule>
@@ -13829,16 +14603,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="G2:G149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Agency,Cleo,Both"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"One-off,Daily,Weekly,Fortnightly,Monthly,Ongoing"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J149" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J156" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Blocked,Done,Not applicable"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16658,6 +17432,1563 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Local citations — the build list</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The Citations tab fixes listings that already exist. This one builds listings where there are none. Decide the record once, then paste it, unchanged, into every form below.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="G2" s="3">
+        <f>COUNTIF(G37:G64,"Done")</f>
+        <v/>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Still to do</t>
+        </is>
+      </c>
+      <c r="I2" s="3">
+        <f>COUNTIF(G37:G64,"Not started")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>THE RECORD — paste this, exactly, every time</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Where it gets decided</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Business name (exact)</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Luxury Beauty by Cleo R.</t>
+        </is>
+      </c>
+      <c r="E6" s="28" t="inlineStr">
+        <is>
+          <t>Use this spelling everywhere. No 'Med Spa', no 'Inc', no variations</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Practitioner</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Cleo Rukovo, NP</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>Nurse practitioner. Some healthcare directories list the person, not the practice</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Address line 1</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>3060 Preserve Drive</t>
+        </is>
+      </c>
+      <c r="E8" s="28" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Suite / unit</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n"/>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>Waiting on the Allure conversation. This is what separates you from their listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Oakville</t>
+        </is>
+      </c>
+      <c r="E10" s="28" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Province</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="E11" s="28" t="inlineStr">
+        <is>
+          <t>Write 'Ontario' in full, or 'ON' — pick one and never mix them</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Postal code</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>L6M 0T9</t>
+        </is>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>NOT L6M 4L9. That is the error on most listings today</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="n"/>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>One number, everywhere. A local 905 or 289 line beats the 416 mobile if you can get one</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="n"/>
+      <c r="E15" s="28" t="inlineStr">
+        <is>
+          <t>One address. Currently split between crukovo@ and luxury.beautyaestheticz@</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>https://luxurybeautybycleo.ca</t>
+        </is>
+      </c>
+      <c r="E16" s="28" t="inlineStr">
+        <is>
+          <t>Use the booking link until the site is live in October, then switch every listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>Booking URL</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="n"/>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>Needed before any directory that offers a booking button</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>Primary category</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="n"/>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>Set on the Google profile first, then match it everywhere else</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Secondary categories</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="n"/>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>Chosen to avoid colliding with Allure's listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Short description (under 250 characters)</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="n"/>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>Names the town and the treatments. No prescription drug names, no benefit claims</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Long description</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="n"/>
+      <c r="E21" s="28" t="inlineStr">
+        <is>
+          <t>Same rules. Write once, reuse everywhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Hours — Monday</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="n"/>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>All seven days. 'Closed' is an answer; blank is not</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Hours — Tuesday</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="n"/>
+      <c r="E23" s="28" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Hours — Wednesday</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="n"/>
+      <c r="E24" s="28" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Hours — Thursday</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="n"/>
+      <c r="E25" s="28" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Hours — Friday</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="n"/>
+      <c r="E26" s="28" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Hours — Saturday</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="n"/>
+      <c r="E27" s="28" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>Hours — Sunday</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="n"/>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>The only hours on record anywhere today are Sunday 12 to 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Year established</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="n"/>
+      <c r="E29" s="28" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>Service area</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Oakville, Burlington, Milton, Mississauga, Glen Abbey, Joshua Creek, Bronte</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>Used where a directory asks for a service radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Logo file</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n"/>
+      <c r="E31" s="28" t="inlineStr">
+        <is>
+          <t>From design/brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>Cover photo</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n"/>
+      <c r="E32" s="28" t="inlineStr">
+        <is>
+          <t>The treatment room or the space, not a stock image</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>Amber means still undecided. Every amber row above has a matching row on the Waiting On Cleo tab. Do not submit to anything below until they are all filled in — a wrong detail submitted 28 times is 28 corrections later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>SUBMISSION QUEUE — one a day in the citation slot, once the record is settled</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Directory</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Where to start</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>Account needed</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Verified live</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>Date submitted</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>Live listing URL</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>NAP checked</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Town of Oakville business directory</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>oakville.ca</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="n"/>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Oakville.com business listing</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>oakville.com</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="21" t="n"/>
+      <c r="K38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Oakville News business listing</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>oakvillenews.org</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="21" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Visit Oakville / tourism listing</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="21" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Halton Region business directory</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>halton.ca</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="21" t="n"/>
+      <c r="K41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Burlington Chamber of Commerce</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="21" t="n"/>
+      <c r="K42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Nextdoor business page, Oakville</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>business.nextdoor.com</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="21" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Nurse Practitioners' Association of Ontario</t>
+        </is>
+      </c>
+      <c r="B44" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>npao.org</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="21" t="n"/>
+      <c r="K44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>College of Nurses of Ontario public register</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>cno.org</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="21" t="n"/>
+      <c r="K45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Opencare</t>
+        </is>
+      </c>
+      <c r="B46" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>opencare.com</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="21" t="n"/>
+      <c r="K46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Doctify Canada</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>doctify.com</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="21" t="n"/>
+      <c r="K47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Vitals / Healthgrades Canada</t>
+        </is>
+      </c>
+      <c r="B48" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="21" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="21" t="n"/>
+      <c r="K48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Booksy</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>booksy.com</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="21" t="n"/>
+      <c r="K49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Vagaro</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>vagaro.com</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="21" t="n"/>
+      <c r="K50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>Spas of America</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>spasofamerica.com</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="21" t="n"/>
+      <c r="K51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Canpages</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C52" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>canpages.ca</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="21" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>ProfileCanada</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>profilecanada.com</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="21" t="n"/>
+      <c r="K53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>n49</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C54" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>n49.com</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="21" t="n"/>
+      <c r="K54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Hotfrog Canada</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C55" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>hotfrog.ca</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Canadian Business Directory</t>
+        </is>
+      </c>
+      <c r="B56" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C56" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="21" t="n"/>
+      <c r="K56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>Where To Canada</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C57" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="21" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="21" t="n"/>
+      <c r="K57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Yably Canada</t>
+        </is>
+      </c>
+      <c r="B58" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>yably.ca</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="21" t="n"/>
+      <c r="K58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Data Axle Canada</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t>Canadian</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="21" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H59" s="22" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="21" t="n"/>
+      <c r="K59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Waze business listing</t>
+        </is>
+      </c>
+      <c r="B60" s="21" t="inlineStr">
+        <is>
+          <t>Maps</t>
+        </is>
+      </c>
+      <c r="C60" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>waze.com</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="21" t="n"/>
+      <c r="K60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Here WeGo</t>
+        </is>
+      </c>
+      <c r="B61" s="21" t="inlineStr">
+        <is>
+          <t>Maps</t>
+        </is>
+      </c>
+      <c r="C61" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>here.com</t>
+        </is>
+      </c>
+      <c r="E61" s="21" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H61" s="22" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="21" t="n"/>
+      <c r="K61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>LinkedIn company page</t>
+        </is>
+      </c>
+      <c r="B62" s="21" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="C62" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>linkedin.com</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="n"/>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="21" t="n"/>
+      <c r="K62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Pinterest business profile</t>
+        </is>
+      </c>
+      <c r="B63" s="21" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="C63" s="21" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>pinterest.com</t>
+        </is>
+      </c>
+      <c r="E63" s="21" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>TikTok business profile</t>
+        </is>
+      </c>
+      <c r="B64" s="21" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="C64" s="21" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>tiktok.com</t>
+        </is>
+      </c>
+      <c r="E64" s="21" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="21" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="21" t="n"/>
+      <c r="K64" s="4" t="n"/>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>Domains in 'Where to start' are a starting point, not gospel. Canadian directories close and change hands. The first pass on every row is confirming it still exists and still takes a free listing — if it does not, set Status to Not applicable and say so in Notes rather than leaving it silent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Google, Yelp.ca, Facebook, Fresha, Yellow Pages, Apple Maps, Bing Places, RateMDs, 411.ca, Cylex, Foursquare and the chamber listings are not repeated here — they already exist and live on the Citations tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Every listing built before the site launches carries the booking link. In launch week, week of 5 October, every one of them gets updated to the live site URL. That is a task on the Tasks tab, not a thing to remember.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A36:K64"/>
+  <mergeCells count="60">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E26:K26"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E16:K16"/>
+    <mergeCell ref="E32:K32"/>
+    <mergeCell ref="E7:K7"/>
+    <mergeCell ref="E25:K25"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E18:K18"/>
+    <mergeCell ref="E21:K21"/>
+    <mergeCell ref="E12:K12"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="E24:K24"/>
+    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="E8:K8"/>
+    <mergeCell ref="E14:K14"/>
+    <mergeCell ref="E17:K17"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E29:K29"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="E20:K20"/>
+    <mergeCell ref="E10:K10"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E28:K28"/>
+    <mergeCell ref="E13:K13"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E9:K9"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E15:K15"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E11:K11"/>
+    <mergeCell ref="A67:K67"/>
+    <mergeCell ref="E27:K27"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B6:B32">
+    <cfRule type="expression" priority="1" dxfId="2" stopIfTrue="0">
+      <formula>$B6=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37:K64">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="0">
+      <formula>$G37="Done"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="0">
+      <formula>$G37="Blocked"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2" stopIfTrue="0">
+      <formula>$G37="In progress"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation sqref="B37:B64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Local,Healthcare,Canadian,Maps,Social"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C37:C64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"High,Medium,Low"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E37:E64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F37:F64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J37:J64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G37:G64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In progress,Blocked,Done,Not applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18158,396 +20489,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monthly numbers</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Fill at the end of each month. Compare against the baseline column, not against last month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>What we track</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Baseline (17 Aug)</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Target by 14 Feb</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>End Sep</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>End Oct</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>End Nov</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>End Dec</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>End Jan</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>Mid Feb</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Google reviews</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>30 to 34, still at or near 5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Google review average</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>At or near 5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Calls from Google profile</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Up on baseline every month</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Direction requests from Google</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Up on baseline every month</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Google profile views</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Up on baseline every month</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>GBP posts published in the month</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>20 or more, every month</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Map pack position: nurse injector oakville</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Visible in the pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Map pack position: botox oakville</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Visible in the pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Map pack position: lip filler oakville</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Visible in the pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Instagram profile visits</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr"/>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Up on baseline</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Instagram link taps</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Rising faster than profile visits</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Reels published in the month</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Four, one a week</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>DMs received</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Not tracked</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Tracked weekly from week 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Consultations booked</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Not tracked</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Tracked weekly, attributed to source</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Ad spend</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Not supplied</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Confirmed and split 70/20/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Cost per DM from ads</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Falling month on month</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Website sessions</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>No site</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>From launch in October, rising month on month</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Search Console impressions</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>No site</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Rising month on month from October</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Pages indexed</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>No site</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Every page, confirmed in Search Console</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Daily slot completion rate</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr"/>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>85 per cent or better</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>